--- a/synthetic/output/representatives/representatives.xlsx
+++ b/synthetic/output/representatives/representatives.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>representative id</t>
+          <t>rep id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -429,22 +429,22 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>last name</t>
+          <t>lastname</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>territory code</t>
+          <t>area code</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>join date</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>active status</t>
+          <t>employee status</t>
         </is>
       </c>
     </row>
@@ -466,17 +466,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>T007</t>
+          <t>T002</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>aishani.bassi1@example.com</t>
+          <t>2025-04-12</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -488,27 +488,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tripti</t>
+          <t>Jeet</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Yadav</t>
+          <t>Radhakrishnan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>T018</t>
+          <t>T015</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>tripti.yadav2@example.com</t>
+          <t>2022-01-08</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -520,27 +520,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jeet</t>
+          <t>Chaaya</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Radhakrishnan</t>
+          <t>Pathak</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>T014</t>
+          <t>T018</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>jeet.radhakrishnan3@example.com</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -552,27 +552,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Farhan</t>
+          <t>Ekaraj</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Memon</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>T008</t>
+          <t>T004</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>farhan.memon4@example.com</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -584,27 +584,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Janaki</t>
+          <t>Bimala</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Handa</t>
+          <t>Buch</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>T015</t>
+          <t>T013</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>janaki.handa5@example.com</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -616,27 +616,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ekaraj</t>
+          <t>Harrison</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Rai</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>T019</t>
+          <t>T003</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ekaraj.bath6@example.com</t>
+          <t>2023-01-07</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -648,27 +648,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vedant</t>
+          <t>Janya</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mann</t>
+          <t>Gaba</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>T009</t>
+          <t>T018</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>vedant.mann7@example.com</t>
+          <t>2023-06-25</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -680,27 +680,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Fariq</t>
+          <t>Shaurya</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kaul</t>
+          <t>Loke</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>T001</t>
+          <t>T010</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>fariq.kaul8@example.com</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -712,27 +712,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Harrison</t>
+          <t>Ekbal</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rai</t>
+          <t>Garg</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>T006</t>
+          <t>T020</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>harrison.rai9@example.com</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -744,27 +744,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Arunima</t>
+          <t>Yash</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Setty</t>
+          <t>Gade</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>T014</t>
+          <t>T012</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>arunima.setty10@example.com</t>
+          <t>2023-12-10</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>Active</t>
         </is>
       </c>
     </row>

--- a/synthetic/output/representatives/representatives.xlsx
+++ b/synthetic/output/representatives/representatives.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,7 +429,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>lastname</t>
+          <t>surname</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -439,7 +439,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>join date</t>
+          <t>date joined</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -456,22 +456,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Aishani</t>
+          <t>Priya</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bassi</t>
+          <t>Rastogi</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>T002</t>
+          <t>T038</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2023-06-10</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -488,22 +488,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jeet</t>
+          <t>Lakshit</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Radhakrishnan</t>
+          <t>Upadhyay</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>T015</t>
+          <t>T026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2022-01-08</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -520,22 +520,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Chaaya</t>
+          <t>Champak</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pathak</t>
+          <t>Choudhary</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>T018</t>
+          <t>T024</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -552,22 +552,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ekaraj</t>
+          <t>Nathaniel</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Sami</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>T004</t>
+          <t>T015</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-08-11</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -584,22 +584,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bimala</t>
+          <t>Lekha</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Buch</t>
+          <t>Raj</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>T013</t>
+          <t>T009</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -616,22 +616,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Harrison</t>
+          <t>Upadhriti</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rai</t>
+          <t>Wadhwa</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>T003</t>
+          <t>T033</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2023-01-07</t>
+          <t>2022-11-20</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -648,22 +648,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Janya</t>
+          <t>Advay</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Gaba</t>
+          <t>Contractor</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>T018</t>
+          <t>T032</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2023-06-25</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -680,22 +680,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Shaurya</t>
+          <t>Amara</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Loke</t>
+          <t>Oak</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>T010</t>
+          <t>T006</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2022-03-09</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -712,22 +712,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ekbal</t>
+          <t>Radhika</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Garg</t>
+          <t>Dugar</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>T020</t>
+          <t>T049</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -744,25 +744,665 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Yash</t>
+          <t>Adya</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Gade</t>
+          <t>Tella</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>T012</t>
+          <t>T004</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2023-12-10</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FR0011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Yashica</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Cherian</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>T008</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FR0012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Chanchal</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Tripathi</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>T010</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>FR0013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Prakash</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>T041</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FR0014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Aadi</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Naik</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>T011</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2024-01-27</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>FR0015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Isaac</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Patil</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>T044</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>FR0016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Damyanti</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Khatri</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>T028</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2021-12-01</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FR0017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Farhan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Chada</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>T039</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>FR0018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ekapad</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Walia</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>T005</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>FR0019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabir</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Soman</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>T025</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>FR0020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Noah</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Lanka</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>T025</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2024-04-08</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>FR0021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Pallavi</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Kakar</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>T039</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>FR0022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Sai</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Muni</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>T030</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2023-08-16</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>FR0023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kashvi</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Sarma</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>T034</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>FR0024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Siya</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Dara</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>T017</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2022-11-13</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>FR0025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Devansh</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Nigam</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>T036</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2021-09-25</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>FR0026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Victor</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Kannan</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>T001</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2021-08-31</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>FR0027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Karnik</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>T044</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2021-12-19</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>FR0028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Azad</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Narayanan</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>T047</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2021-12-25</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>FR0029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Wazir</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Mallick</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>T008</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2024-12-22</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>FR0030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Tanish</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Zacharia</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>T044</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2022-04-16</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
